--- a/mom/docs/forms/frm-700-maintenance/FRM-703_WIP_Tag.xlsx
+++ b/mom/docs/forms/frm-700-maintenance/FRM-703_WIP_Tag.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM_703" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="FRM_703" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="LISTS" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="83">
+  <fonts count="84">
     <font>
       <name val="Arial"/>
       <family val="2"/>
@@ -484,6 +484,12 @@
     </font>
     <font>
       <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
       <color rgb="00CBD5E1"/>
       <sz val="8"/>
     </font>
@@ -493,7 +499,7 @@
       <sz val="6"/>
     </font>
   </fonts>
-  <fills count="50">
+  <fills count="52">
     <fill>
       <patternFill/>
     </fill>
@@ -743,8 +749,20 @@
         <bgColor rgb="00F1F5F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00005A9E"/>
+        <bgColor rgb="00005A9E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="247">
+  <borders count="258">
     <border>
       <left/>
       <right/>
@@ -3514,26 +3532,120 @@
         <color rgb="000078D4"/>
       </left>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
         <color rgb="000078D4"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
+      </right>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="000078D4"/>
-      </bottom>
-      <diagonal/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right/>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <bottom/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="502">
+  <cellXfs count="517">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -4724,20 +4836,53 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="244" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="50" borderId="222" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="50" borderId="220" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="50" borderId="221" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="49" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="246" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="246" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="47" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="47" borderId="248" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="246" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="49" borderId="254" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="47" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="47" borderId="253" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="79" fillId="49" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="47" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="82" fillId="47" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="214" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="215" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="245" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="255" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="235" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="246" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="48" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="256" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="83" fillId="48" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="257" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4820,52 +4965,40 @@
     <author>QMS</author>
   </authors>
   <commentList>
-    <comment ref="A9" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Số Job
-</t>
-      </text>
-    </comment>
-    <comment ref="U9" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Mã chi tiết
-</t>
-      </text>
-    </comment>
-    <comment ref="A10" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Số lượng
-</t>
-      </text>
-    </comment>
-    <comment ref="U10" authorId="0" shapeId="0">
-      <text>
-        <t>Nguyên công
-Operation hiện tại.</t>
-      </text>
-    </comment>
-    <comment ref="A11" authorId="0" shapeId="0">
-      <text>
-        <t>Máy
-Máy đang chạy.</t>
-      </text>
-    </comment>
-    <comment ref="U11" authorId="0" shapeId="0">
-      <text>
-        <t>Trạng thái
-IN PROCESS / HOLD / WAITING / COMPLETE.</t>
-      </text>
-    </comment>
     <comment ref="A12" authorId="0" shapeId="0">
       <text>
-        <t xml:space="preserve">Operator
-</t>
+        <t>Số lượng trong khay
+Số chi tiết thực tế trong khay/thùng — đếm và ghi chính xác.</t>
       </text>
     </comment>
     <comment ref="U12" authorId="0" shapeId="0">
       <text>
-        <t xml:space="preserve">Ngày
-</t>
+        <t>Lô / số mẻ (heat)
+Lô hoặc số heat vật liệu — truy về FRM-414 chứng chỉ vật tư.</t>
+      </text>
+    </comment>
+    <comment ref="A17" authorId="0" shapeId="0">
+      <text>
+        <t>Khay xanh dương
+Đánh dấu khi sản phẩm đang gia công hoặc chờ kiểm tra.</t>
+      </text>
+    </comment>
+    <comment ref="A18" authorId="0" shapeId="0">
+      <text>
+        <t>Khay vàng
+Đánh dấu khi hàng lỗi đang chờ xác nhận / chờ sửa.</t>
+      </text>
+    </comment>
+    <comment ref="A19" authorId="0" shapeId="0">
+      <text>
+        <t>Khay đỏ
+Đánh dấu khi hàng NG — phải đưa về khu cách ly NG.</t>
+      </text>
+    </comment>
+    <comment ref="A27" authorId="0" shapeId="0">
+      <text>
+        <t>Lịch sử đổi trạng thái
+Mỗi dòng = một lần đổi màu khay / trạng thái sản phẩm.</t>
       </text>
     </comment>
   </commentList>
@@ -4873,7 +5006,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -4888,13 +5021,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5191,7 +5327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:AN20"/>
+  <dimension ref="A2:AN41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.375" customWidth="1" style="264" min="1" max="1"/>
@@ -5248,7 +5384,7 @@
       <c r="H2" s="274" t="n"/>
       <c r="I2" s="289" t="inlineStr">
         <is>
-          <t>WIP TAG</t>
+          <t>WIP / PRODUCT IDENTIFICATION TAG</t>
         </is>
       </c>
       <c r="J2" s="274" t="n"/>
@@ -5347,7 +5483,7 @@
       <c r="AH4" s="15" t="n"/>
       <c r="AI4" s="293" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="AJ4" s="14" t="n"/>
@@ -5373,7 +5509,7 @@
       <c r="AH5" s="15" t="n"/>
       <c r="AI5" s="293" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Warehouse / Production</t>
         </is>
       </c>
       <c r="AJ5" s="14" t="n"/>
@@ -5427,7 +5563,7 @@
       <c r="AH6" s="270" t="n"/>
       <c r="AI6" s="295" t="inlineStr">
         <is>
-          <t>Production Supervisor</t>
+          <t>QA Manager</t>
         </is>
       </c>
       <c r="AJ6" s="268" t="n"/>
@@ -5437,7 +5573,7 @@
       <c r="AN6" s="272" t="n"/>
     </row>
     <row r="7" ht="4" customHeight="1" s="264">
-      <c r="A7" s="469" t="n"/>
+      <c r="A7" s="516" t="n"/>
       <c r="B7" s="26" t="n"/>
       <c r="C7" s="26" t="n"/>
       <c r="D7" s="26" t="n"/>
@@ -5481,7 +5617,7 @@
     <row r="8" ht="17" customHeight="1" s="264">
       <c r="A8" s="470" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.  REFERENCE INFORMATION</t>
+          <t xml:space="preserve">  1.  PRODUCT IDENTIFICATION</t>
         </is>
       </c>
       <c r="B8" s="471" t="n"/>
@@ -5527,7 +5663,7 @@
     <row r="9" ht="20" customHeight="1" s="264">
       <c r="A9" s="473" t="inlineStr">
         <is>
-          <t>Job / WO</t>
+          <t>Part No. / Rev</t>
         </is>
       </c>
       <c r="B9" s="474" t="n"/>
@@ -5551,7 +5687,7 @@
       <c r="T9" s="475" t="n"/>
       <c r="U9" s="477" t="inlineStr">
         <is>
-          <t>Part No. / Rev</t>
+          <t>Part Name</t>
         </is>
       </c>
       <c r="V9" s="474" t="n"/>
@@ -5577,7 +5713,7 @@
     <row r="10" ht="20" customHeight="1" s="264">
       <c r="A10" s="480" t="inlineStr">
         <is>
-          <t>Qty</t>
+          <t>Job / WO</t>
         </is>
       </c>
       <c r="B10" s="481" t="n"/>
@@ -5601,7 +5737,7 @@
       <c r="T10" s="482" t="n"/>
       <c r="U10" s="484" t="inlineStr">
         <is>
-          <t>Operation / Step</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="V10" s="481" t="n"/>
@@ -5627,7 +5763,7 @@
     <row r="11" ht="20" customHeight="1" s="264">
       <c r="A11" s="480" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Current Operation</t>
         </is>
       </c>
       <c r="B11" s="481" t="n"/>
@@ -5651,7 +5787,7 @@
       <c r="T11" s="482" t="n"/>
       <c r="U11" s="484" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Next Operation</t>
         </is>
       </c>
       <c r="V11" s="481" t="n"/>
@@ -5675,421 +5811,1513 @@
       <c r="AN11" s="486" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="264">
-      <c r="A12" s="487" t="inlineStr">
+      <c r="A12" s="480" t="inlineStr">
+        <is>
+          <t>Qty in Tray / Container</t>
+        </is>
+      </c>
+      <c r="B12" s="481" t="n"/>
+      <c r="C12" s="481" t="n"/>
+      <c r="D12" s="481" t="n"/>
+      <c r="E12" s="481" t="n"/>
+      <c r="F12" s="481" t="n"/>
+      <c r="G12" s="482" t="n"/>
+      <c r="H12" s="483" t="n"/>
+      <c r="I12" s="481" t="n"/>
+      <c r="J12" s="481" t="n"/>
+      <c r="K12" s="481" t="n"/>
+      <c r="L12" s="481" t="n"/>
+      <c r="M12" s="481" t="n"/>
+      <c r="N12" s="481" t="n"/>
+      <c r="O12" s="481" t="n"/>
+      <c r="P12" s="481" t="n"/>
+      <c r="Q12" s="481" t="n"/>
+      <c r="R12" s="481" t="n"/>
+      <c r="S12" s="481" t="n"/>
+      <c r="T12" s="482" t="n"/>
+      <c r="U12" s="484" t="inlineStr">
+        <is>
+          <t>Lot / Heat No.</t>
+        </is>
+      </c>
+      <c r="V12" s="481" t="n"/>
+      <c r="W12" s="481" t="n"/>
+      <c r="X12" s="481" t="n"/>
+      <c r="Y12" s="481" t="n"/>
+      <c r="Z12" s="481" t="n"/>
+      <c r="AA12" s="482" t="n"/>
+      <c r="AB12" s="485" t="n"/>
+      <c r="AC12" s="481" t="n"/>
+      <c r="AD12" s="481" t="n"/>
+      <c r="AE12" s="481" t="n"/>
+      <c r="AF12" s="481" t="n"/>
+      <c r="AG12" s="481" t="n"/>
+      <c r="AH12" s="481" t="n"/>
+      <c r="AI12" s="481" t="n"/>
+      <c r="AJ12" s="481" t="n"/>
+      <c r="AK12" s="481" t="n"/>
+      <c r="AL12" s="481" t="n"/>
+      <c r="AM12" s="481" t="n"/>
+      <c r="AN12" s="486" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1" s="264">
+      <c r="A13" s="480" t="inlineStr">
+        <is>
+          <t>Material / Spec</t>
+        </is>
+      </c>
+      <c r="B13" s="481" t="n"/>
+      <c r="C13" s="481" t="n"/>
+      <c r="D13" s="481" t="n"/>
+      <c r="E13" s="481" t="n"/>
+      <c r="F13" s="481" t="n"/>
+      <c r="G13" s="482" t="n"/>
+      <c r="H13" s="483" t="n"/>
+      <c r="I13" s="481" t="n"/>
+      <c r="J13" s="481" t="n"/>
+      <c r="K13" s="481" t="n"/>
+      <c r="L13" s="481" t="n"/>
+      <c r="M13" s="481" t="n"/>
+      <c r="N13" s="481" t="n"/>
+      <c r="O13" s="481" t="n"/>
+      <c r="P13" s="481" t="n"/>
+      <c r="Q13" s="481" t="n"/>
+      <c r="R13" s="481" t="n"/>
+      <c r="S13" s="481" t="n"/>
+      <c r="T13" s="482" t="n"/>
+      <c r="U13" s="484" t="inlineStr">
+        <is>
+          <t>Drawing Rev</t>
+        </is>
+      </c>
+      <c r="V13" s="481" t="n"/>
+      <c r="W13" s="481" t="n"/>
+      <c r="X13" s="481" t="n"/>
+      <c r="Y13" s="481" t="n"/>
+      <c r="Z13" s="481" t="n"/>
+      <c r="AA13" s="482" t="n"/>
+      <c r="AB13" s="485" t="n"/>
+      <c r="AC13" s="481" t="n"/>
+      <c r="AD13" s="481" t="n"/>
+      <c r="AE13" s="481" t="n"/>
+      <c r="AF13" s="481" t="n"/>
+      <c r="AG13" s="481" t="n"/>
+      <c r="AH13" s="481" t="n"/>
+      <c r="AI13" s="481" t="n"/>
+      <c r="AJ13" s="481" t="n"/>
+      <c r="AK13" s="481" t="n"/>
+      <c r="AL13" s="481" t="n"/>
+      <c r="AM13" s="481" t="n"/>
+      <c r="AN13" s="486" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1" s="264">
+      <c r="A14" s="487" t="inlineStr">
         <is>
           <t>Operator</t>
         </is>
       </c>
-      <c r="B12" s="488" t="n"/>
-      <c r="C12" s="488" t="n"/>
-      <c r="D12" s="488" t="n"/>
-      <c r="E12" s="488" t="n"/>
-      <c r="F12" s="488" t="n"/>
-      <c r="G12" s="489" t="n"/>
-      <c r="H12" s="490" t="n"/>
-      <c r="I12" s="488" t="n"/>
-      <c r="J12" s="488" t="n"/>
-      <c r="K12" s="488" t="n"/>
-      <c r="L12" s="488" t="n"/>
-      <c r="M12" s="488" t="n"/>
-      <c r="N12" s="488" t="n"/>
-      <c r="O12" s="488" t="n"/>
-      <c r="P12" s="488" t="n"/>
-      <c r="Q12" s="488" t="n"/>
-      <c r="R12" s="488" t="n"/>
-      <c r="S12" s="488" t="n"/>
-      <c r="T12" s="489" t="n"/>
-      <c r="U12" s="491" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="V12" s="488" t="n"/>
-      <c r="W12" s="488" t="n"/>
-      <c r="X12" s="488" t="n"/>
-      <c r="Y12" s="488" t="n"/>
-      <c r="Z12" s="488" t="n"/>
-      <c r="AA12" s="489" t="n"/>
-      <c r="AB12" s="492" t="n"/>
-      <c r="AC12" s="488" t="n"/>
-      <c r="AD12" s="488" t="n"/>
-      <c r="AE12" s="488" t="n"/>
-      <c r="AF12" s="488" t="n"/>
-      <c r="AG12" s="488" t="n"/>
-      <c r="AH12" s="488" t="n"/>
-      <c r="AI12" s="488" t="n"/>
-      <c r="AJ12" s="488" t="n"/>
-      <c r="AK12" s="488" t="n"/>
-      <c r="AL12" s="488" t="n"/>
-      <c r="AM12" s="488" t="n"/>
-      <c r="AN12" s="493" t="n"/>
+      <c r="B14" s="488" t="n"/>
+      <c r="C14" s="488" t="n"/>
+      <c r="D14" s="488" t="n"/>
+      <c r="E14" s="488" t="n"/>
+      <c r="F14" s="488" t="n"/>
+      <c r="G14" s="489" t="n"/>
+      <c r="H14" s="490" t="n"/>
+      <c r="I14" s="488" t="n"/>
+      <c r="J14" s="488" t="n"/>
+      <c r="K14" s="488" t="n"/>
+      <c r="L14" s="488" t="n"/>
+      <c r="M14" s="488" t="n"/>
+      <c r="N14" s="488" t="n"/>
+      <c r="O14" s="488" t="n"/>
+      <c r="P14" s="488" t="n"/>
+      <c r="Q14" s="488" t="n"/>
+      <c r="R14" s="488" t="n"/>
+      <c r="S14" s="488" t="n"/>
+      <c r="T14" s="489" t="n"/>
+      <c r="U14" s="491" t="inlineStr">
+        <is>
+          <t>Date / Shift</t>
+        </is>
+      </c>
+      <c r="V14" s="488" t="n"/>
+      <c r="W14" s="488" t="n"/>
+      <c r="X14" s="488" t="n"/>
+      <c r="Y14" s="488" t="n"/>
+      <c r="Z14" s="488" t="n"/>
+      <c r="AA14" s="489" t="n"/>
+      <c r="AB14" s="492" t="n"/>
+      <c r="AC14" s="488" t="n"/>
+      <c r="AD14" s="488" t="n"/>
+      <c r="AE14" s="488" t="n"/>
+      <c r="AF14" s="488" t="n"/>
+      <c r="AG14" s="488" t="n"/>
+      <c r="AH14" s="488" t="n"/>
+      <c r="AI14" s="488" t="n"/>
+      <c r="AJ14" s="488" t="n"/>
+      <c r="AK14" s="488" t="n"/>
+      <c r="AL14" s="488" t="n"/>
+      <c r="AM14" s="488" t="n"/>
+      <c r="AN14" s="493" t="n"/>
     </row>
-    <row r="13" ht="4" customHeight="1" s="264">
-      <c r="A13" s="469" t="n"/>
-      <c r="B13" s="26" t="n"/>
-      <c r="C13" s="26" t="n"/>
-      <c r="D13" s="26" t="n"/>
-      <c r="E13" s="26" t="n"/>
-      <c r="F13" s="26" t="n"/>
-      <c r="G13" s="26" t="n"/>
-      <c r="H13" s="26" t="n"/>
-      <c r="I13" s="26" t="n"/>
-      <c r="J13" s="26" t="n"/>
-      <c r="K13" s="26" t="n"/>
-      <c r="L13" s="26" t="n"/>
-      <c r="M13" s="26" t="n"/>
-      <c r="N13" s="26" t="n"/>
-      <c r="O13" s="26" t="n"/>
-      <c r="P13" s="26" t="n"/>
-      <c r="Q13" s="26" t="n"/>
-      <c r="R13" s="26" t="n"/>
-      <c r="S13" s="26" t="n"/>
-      <c r="T13" s="26" t="n"/>
-      <c r="U13" s="26" t="n"/>
-      <c r="V13" s="26" t="n"/>
-      <c r="W13" s="26" t="n"/>
-      <c r="X13" s="26" t="n"/>
-      <c r="Y13" s="26" t="n"/>
-      <c r="Z13" s="26" t="n"/>
-      <c r="AA13" s="26" t="n"/>
-      <c r="AB13" s="26" t="n"/>
-      <c r="AC13" s="26" t="n"/>
-      <c r="AD13" s="26" t="n"/>
-      <c r="AE13" s="26" t="n"/>
-      <c r="AF13" s="26" t="n"/>
-      <c r="AG13" s="26" t="n"/>
-      <c r="AH13" s="26" t="n"/>
-      <c r="AI13" s="26" t="n"/>
-      <c r="AJ13" s="26" t="n"/>
-      <c r="AK13" s="26" t="n"/>
-      <c r="AL13" s="26" t="n"/>
-      <c r="AM13" s="26" t="n"/>
-      <c r="AN13" s="26" t="n"/>
+    <row r="15" ht="4" customHeight="1" s="264">
+      <c r="A15" s="516" t="n"/>
+      <c r="B15" s="26" t="n"/>
+      <c r="C15" s="26" t="n"/>
+      <c r="D15" s="26" t="n"/>
+      <c r="E15" s="26" t="n"/>
+      <c r="F15" s="26" t="n"/>
+      <c r="G15" s="26" t="n"/>
+      <c r="H15" s="26" t="n"/>
+      <c r="I15" s="26" t="n"/>
+      <c r="J15" s="26" t="n"/>
+      <c r="K15" s="26" t="n"/>
+      <c r="L15" s="26" t="n"/>
+      <c r="M15" s="26" t="n"/>
+      <c r="N15" s="26" t="n"/>
+      <c r="O15" s="26" t="n"/>
+      <c r="P15" s="26" t="n"/>
+      <c r="Q15" s="26" t="n"/>
+      <c r="R15" s="26" t="n"/>
+      <c r="S15" s="26" t="n"/>
+      <c r="T15" s="26" t="n"/>
+      <c r="U15" s="26" t="n"/>
+      <c r="V15" s="26" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="26" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="26" t="n"/>
+      <c r="AB15" s="26" t="n"/>
+      <c r="AC15" s="26" t="n"/>
+      <c r="AD15" s="26" t="n"/>
+      <c r="AE15" s="26" t="n"/>
+      <c r="AF15" s="26" t="n"/>
+      <c r="AG15" s="26" t="n"/>
+      <c r="AH15" s="26" t="n"/>
+      <c r="AI15" s="26" t="n"/>
+      <c r="AJ15" s="26" t="n"/>
+      <c r="AK15" s="26" t="n"/>
+      <c r="AL15" s="26" t="n"/>
+      <c r="AM15" s="26" t="n"/>
+      <c r="AN15" s="26" t="n"/>
     </row>
-    <row r="14" ht="17" customHeight="1" s="264">
-      <c r="A14" s="470" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2.  APPROVAL</t>
-        </is>
-      </c>
-      <c r="B14" s="471" t="n"/>
-      <c r="C14" s="471" t="n"/>
-      <c r="D14" s="471" t="n"/>
-      <c r="E14" s="471" t="n"/>
-      <c r="F14" s="471" t="n"/>
-      <c r="G14" s="471" t="n"/>
-      <c r="H14" s="471" t="n"/>
-      <c r="I14" s="471" t="n"/>
-      <c r="J14" s="471" t="n"/>
-      <c r="K14" s="471" t="n"/>
-      <c r="L14" s="471" t="n"/>
-      <c r="M14" s="471" t="n"/>
-      <c r="N14" s="471" t="n"/>
-      <c r="O14" s="471" t="n"/>
-      <c r="P14" s="471" t="n"/>
-      <c r="Q14" s="471" t="n"/>
-      <c r="R14" s="471" t="n"/>
-      <c r="S14" s="471" t="n"/>
-      <c r="T14" s="471" t="n"/>
-      <c r="U14" s="471" t="n"/>
-      <c r="V14" s="471" t="n"/>
-      <c r="W14" s="471" t="n"/>
-      <c r="X14" s="471" t="n"/>
-      <c r="Y14" s="471" t="n"/>
-      <c r="Z14" s="471" t="n"/>
-      <c r="AA14" s="471" t="n"/>
-      <c r="AB14" s="471" t="n"/>
-      <c r="AC14" s="471" t="n"/>
-      <c r="AD14" s="471" t="n"/>
-      <c r="AE14" s="471" t="n"/>
-      <c r="AF14" s="471" t="n"/>
-      <c r="AG14" s="471" t="n"/>
-      <c r="AH14" s="471" t="n"/>
-      <c r="AI14" s="471" t="n"/>
-      <c r="AJ14" s="471" t="n"/>
-      <c r="AK14" s="471" t="n"/>
-      <c r="AL14" s="471" t="n"/>
-      <c r="AM14" s="471" t="n"/>
-      <c r="AN14" s="472" t="n"/>
+    <row r="16" ht="17" customHeight="1" s="264">
+      <c r="A16" s="470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2.  TRAY STATUS — MARK ONE (per WI-703)</t>
+        </is>
+      </c>
+      <c r="B16" s="471" t="n"/>
+      <c r="C16" s="471" t="n"/>
+      <c r="D16" s="471" t="n"/>
+      <c r="E16" s="471" t="n"/>
+      <c r="F16" s="471" t="n"/>
+      <c r="G16" s="471" t="n"/>
+      <c r="H16" s="471" t="n"/>
+      <c r="I16" s="471" t="n"/>
+      <c r="J16" s="471" t="n"/>
+      <c r="K16" s="471" t="n"/>
+      <c r="L16" s="471" t="n"/>
+      <c r="M16" s="471" t="n"/>
+      <c r="N16" s="471" t="n"/>
+      <c r="O16" s="471" t="n"/>
+      <c r="P16" s="471" t="n"/>
+      <c r="Q16" s="471" t="n"/>
+      <c r="R16" s="471" t="n"/>
+      <c r="S16" s="471" t="n"/>
+      <c r="T16" s="471" t="n"/>
+      <c r="U16" s="471" t="n"/>
+      <c r="V16" s="471" t="n"/>
+      <c r="W16" s="471" t="n"/>
+      <c r="X16" s="471" t="n"/>
+      <c r="Y16" s="471" t="n"/>
+      <c r="Z16" s="471" t="n"/>
+      <c r="AA16" s="471" t="n"/>
+      <c r="AB16" s="471" t="n"/>
+      <c r="AC16" s="471" t="n"/>
+      <c r="AD16" s="471" t="n"/>
+      <c r="AE16" s="471" t="n"/>
+      <c r="AF16" s="471" t="n"/>
+      <c r="AG16" s="471" t="n"/>
+      <c r="AH16" s="471" t="n"/>
+      <c r="AI16" s="471" t="n"/>
+      <c r="AJ16" s="471" t="n"/>
+      <c r="AK16" s="471" t="n"/>
+      <c r="AL16" s="471" t="n"/>
+      <c r="AM16" s="471" t="n"/>
+      <c r="AN16" s="472" t="n"/>
     </row>
-    <row r="15" ht="17" customHeight="1" s="264">
-      <c r="A15" s="494" t="inlineStr">
+    <row r="17" ht="20" customHeight="1" s="264">
+      <c r="A17" s="473" t="inlineStr">
+        <is>
+          <t>XANH DƯƠNG — Đang gia công / Chờ kiểm tra</t>
+        </is>
+      </c>
+      <c r="B17" s="474" t="n"/>
+      <c r="C17" s="474" t="n"/>
+      <c r="D17" s="474" t="n"/>
+      <c r="E17" s="474" t="n"/>
+      <c r="F17" s="474" t="n"/>
+      <c r="G17" s="475" t="n"/>
+      <c r="H17" s="476" t="n"/>
+      <c r="I17" s="474" t="n"/>
+      <c r="J17" s="474" t="n"/>
+      <c r="K17" s="474" t="n"/>
+      <c r="L17" s="474" t="n"/>
+      <c r="M17" s="474" t="n"/>
+      <c r="N17" s="474" t="n"/>
+      <c r="O17" s="474" t="n"/>
+      <c r="P17" s="474" t="n"/>
+      <c r="Q17" s="474" t="n"/>
+      <c r="R17" s="474" t="n"/>
+      <c r="S17" s="474" t="n"/>
+      <c r="T17" s="475" t="n"/>
+      <c r="U17" s="477" t="inlineStr">
+        <is>
+          <t>Tình trạng: sản phẩm trong quá trình sản xuất</t>
+        </is>
+      </c>
+      <c r="V17" s="474" t="n"/>
+      <c r="W17" s="474" t="n"/>
+      <c r="X17" s="474" t="n"/>
+      <c r="Y17" s="474" t="n"/>
+      <c r="Z17" s="474" t="n"/>
+      <c r="AA17" s="475" t="n"/>
+      <c r="AB17" s="478" t="n"/>
+      <c r="AC17" s="474" t="n"/>
+      <c r="AD17" s="474" t="n"/>
+      <c r="AE17" s="474" t="n"/>
+      <c r="AF17" s="474" t="n"/>
+      <c r="AG17" s="474" t="n"/>
+      <c r="AH17" s="474" t="n"/>
+      <c r="AI17" s="474" t="n"/>
+      <c r="AJ17" s="474" t="n"/>
+      <c r="AK17" s="474" t="n"/>
+      <c r="AL17" s="474" t="n"/>
+      <c r="AM17" s="474" t="n"/>
+      <c r="AN17" s="479" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1" s="264">
+      <c r="A18" s="480" t="inlineStr">
+        <is>
+          <t>VÀNG — Hàng lỗi / Chờ xác nhận / Chờ sửa</t>
+        </is>
+      </c>
+      <c r="B18" s="481" t="n"/>
+      <c r="C18" s="481" t="n"/>
+      <c r="D18" s="481" t="n"/>
+      <c r="E18" s="481" t="n"/>
+      <c r="F18" s="481" t="n"/>
+      <c r="G18" s="482" t="n"/>
+      <c r="H18" s="483" t="n"/>
+      <c r="I18" s="481" t="n"/>
+      <c r="J18" s="481" t="n"/>
+      <c r="K18" s="481" t="n"/>
+      <c r="L18" s="481" t="n"/>
+      <c r="M18" s="481" t="n"/>
+      <c r="N18" s="481" t="n"/>
+      <c r="O18" s="481" t="n"/>
+      <c r="P18" s="481" t="n"/>
+      <c r="Q18" s="481" t="n"/>
+      <c r="R18" s="481" t="n"/>
+      <c r="S18" s="481" t="n"/>
+      <c r="T18" s="482" t="n"/>
+      <c r="U18" s="484" t="inlineStr">
+        <is>
+          <t>Tình trạng: chờ QC xác nhận hoặc chờ sửa</t>
+        </is>
+      </c>
+      <c r="V18" s="481" t="n"/>
+      <c r="W18" s="481" t="n"/>
+      <c r="X18" s="481" t="n"/>
+      <c r="Y18" s="481" t="n"/>
+      <c r="Z18" s="481" t="n"/>
+      <c r="AA18" s="482" t="n"/>
+      <c r="AB18" s="485" t="n"/>
+      <c r="AC18" s="481" t="n"/>
+      <c r="AD18" s="481" t="n"/>
+      <c r="AE18" s="481" t="n"/>
+      <c r="AF18" s="481" t="n"/>
+      <c r="AG18" s="481" t="n"/>
+      <c r="AH18" s="481" t="n"/>
+      <c r="AI18" s="481" t="n"/>
+      <c r="AJ18" s="481" t="n"/>
+      <c r="AK18" s="481" t="n"/>
+      <c r="AL18" s="481" t="n"/>
+      <c r="AM18" s="481" t="n"/>
+      <c r="AN18" s="486" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1" s="264">
+      <c r="A19" s="487" t="inlineStr">
+        <is>
+          <t>ĐỎ — Hàng không phù hợp (NG) — Cách ly</t>
+        </is>
+      </c>
+      <c r="B19" s="488" t="n"/>
+      <c r="C19" s="488" t="n"/>
+      <c r="D19" s="488" t="n"/>
+      <c r="E19" s="488" t="n"/>
+      <c r="F19" s="488" t="n"/>
+      <c r="G19" s="489" t="n"/>
+      <c r="H19" s="490" t="n"/>
+      <c r="I19" s="488" t="n"/>
+      <c r="J19" s="488" t="n"/>
+      <c r="K19" s="488" t="n"/>
+      <c r="L19" s="488" t="n"/>
+      <c r="M19" s="488" t="n"/>
+      <c r="N19" s="488" t="n"/>
+      <c r="O19" s="488" t="n"/>
+      <c r="P19" s="488" t="n"/>
+      <c r="Q19" s="488" t="n"/>
+      <c r="R19" s="488" t="n"/>
+      <c r="S19" s="488" t="n"/>
+      <c r="T19" s="489" t="n"/>
+      <c r="U19" s="491" t="inlineStr">
+        <is>
+          <t>Tình trạng: hàng NG, để khu cách ly</t>
+        </is>
+      </c>
+      <c r="V19" s="488" t="n"/>
+      <c r="W19" s="488" t="n"/>
+      <c r="X19" s="488" t="n"/>
+      <c r="Y19" s="488" t="n"/>
+      <c r="Z19" s="488" t="n"/>
+      <c r="AA19" s="489" t="n"/>
+      <c r="AB19" s="492" t="n"/>
+      <c r="AC19" s="488" t="n"/>
+      <c r="AD19" s="488" t="n"/>
+      <c r="AE19" s="488" t="n"/>
+      <c r="AF19" s="488" t="n"/>
+      <c r="AG19" s="488" t="n"/>
+      <c r="AH19" s="488" t="n"/>
+      <c r="AI19" s="488" t="n"/>
+      <c r="AJ19" s="488" t="n"/>
+      <c r="AK19" s="488" t="n"/>
+      <c r="AL19" s="488" t="n"/>
+      <c r="AM19" s="488" t="n"/>
+      <c r="AN19" s="493" t="n"/>
+    </row>
+    <row r="20" ht="4" customHeight="1" s="264">
+      <c r="A20" s="516" t="n"/>
+      <c r="B20" s="26" t="n"/>
+      <c r="C20" s="26" t="n"/>
+      <c r="D20" s="26" t="n"/>
+      <c r="E20" s="26" t="n"/>
+      <c r="F20" s="26" t="n"/>
+      <c r="G20" s="26" t="n"/>
+      <c r="H20" s="26" t="n"/>
+      <c r="I20" s="26" t="n"/>
+      <c r="J20" s="26" t="n"/>
+      <c r="K20" s="26" t="n"/>
+      <c r="L20" s="26" t="n"/>
+      <c r="M20" s="26" t="n"/>
+      <c r="N20" s="26" t="n"/>
+      <c r="O20" s="26" t="n"/>
+      <c r="P20" s="26" t="n"/>
+      <c r="Q20" s="26" t="n"/>
+      <c r="R20" s="26" t="n"/>
+      <c r="S20" s="26" t="n"/>
+      <c r="T20" s="26" t="n"/>
+      <c r="U20" s="26" t="n"/>
+      <c r="V20" s="26" t="n"/>
+      <c r="W20" s="26" t="n"/>
+      <c r="X20" s="26" t="n"/>
+      <c r="Y20" s="26" t="n"/>
+      <c r="Z20" s="26" t="n"/>
+      <c r="AA20" s="26" t="n"/>
+      <c r="AB20" s="26" t="n"/>
+      <c r="AC20" s="26" t="n"/>
+      <c r="AD20" s="26" t="n"/>
+      <c r="AE20" s="26" t="n"/>
+      <c r="AF20" s="26" t="n"/>
+      <c r="AG20" s="26" t="n"/>
+      <c r="AH20" s="26" t="n"/>
+      <c r="AI20" s="26" t="n"/>
+      <c r="AJ20" s="26" t="n"/>
+      <c r="AK20" s="26" t="n"/>
+      <c r="AL20" s="26" t="n"/>
+      <c r="AM20" s="26" t="n"/>
+      <c r="AN20" s="26" t="n"/>
+    </row>
+    <row r="21" ht="17" customHeight="1" s="264">
+      <c r="A21" s="470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3.  QUALITY STATUS &amp; TRACEABILITY</t>
+        </is>
+      </c>
+      <c r="B21" s="471" t="n"/>
+      <c r="C21" s="471" t="n"/>
+      <c r="D21" s="471" t="n"/>
+      <c r="E21" s="471" t="n"/>
+      <c r="F21" s="471" t="n"/>
+      <c r="G21" s="471" t="n"/>
+      <c r="H21" s="471" t="n"/>
+      <c r="I21" s="471" t="n"/>
+      <c r="J21" s="471" t="n"/>
+      <c r="K21" s="471" t="n"/>
+      <c r="L21" s="471" t="n"/>
+      <c r="M21" s="471" t="n"/>
+      <c r="N21" s="471" t="n"/>
+      <c r="O21" s="471" t="n"/>
+      <c r="P21" s="471" t="n"/>
+      <c r="Q21" s="471" t="n"/>
+      <c r="R21" s="471" t="n"/>
+      <c r="S21" s="471" t="n"/>
+      <c r="T21" s="471" t="n"/>
+      <c r="U21" s="471" t="n"/>
+      <c r="V21" s="471" t="n"/>
+      <c r="W21" s="471" t="n"/>
+      <c r="X21" s="471" t="n"/>
+      <c r="Y21" s="471" t="n"/>
+      <c r="Z21" s="471" t="n"/>
+      <c r="AA21" s="471" t="n"/>
+      <c r="AB21" s="471" t="n"/>
+      <c r="AC21" s="471" t="n"/>
+      <c r="AD21" s="471" t="n"/>
+      <c r="AE21" s="471" t="n"/>
+      <c r="AF21" s="471" t="n"/>
+      <c r="AG21" s="471" t="n"/>
+      <c r="AH21" s="471" t="n"/>
+      <c r="AI21" s="471" t="n"/>
+      <c r="AJ21" s="471" t="n"/>
+      <c r="AK21" s="471" t="n"/>
+      <c r="AL21" s="471" t="n"/>
+      <c r="AM21" s="471" t="n"/>
+      <c r="AN21" s="472" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1" s="264">
+      <c r="A22" s="473" t="inlineStr">
+        <is>
+          <t>Inspection Result (FRM-622)</t>
+        </is>
+      </c>
+      <c r="B22" s="474" t="n"/>
+      <c r="C22" s="474" t="n"/>
+      <c r="D22" s="474" t="n"/>
+      <c r="E22" s="474" t="n"/>
+      <c r="F22" s="474" t="n"/>
+      <c r="G22" s="475" t="n"/>
+      <c r="H22" s="476" t="n"/>
+      <c r="I22" s="474" t="n"/>
+      <c r="J22" s="474" t="n"/>
+      <c r="K22" s="474" t="n"/>
+      <c r="L22" s="474" t="n"/>
+      <c r="M22" s="474" t="n"/>
+      <c r="N22" s="474" t="n"/>
+      <c r="O22" s="474" t="n"/>
+      <c r="P22" s="474" t="n"/>
+      <c r="Q22" s="474" t="n"/>
+      <c r="R22" s="474" t="n"/>
+      <c r="S22" s="474" t="n"/>
+      <c r="T22" s="475" t="n"/>
+      <c r="U22" s="477" t="inlineStr">
+        <is>
+          <t>QC Inspector</t>
+        </is>
+      </c>
+      <c r="V22" s="474" t="n"/>
+      <c r="W22" s="474" t="n"/>
+      <c r="X22" s="474" t="n"/>
+      <c r="Y22" s="474" t="n"/>
+      <c r="Z22" s="474" t="n"/>
+      <c r="AA22" s="475" t="n"/>
+      <c r="AB22" s="478" t="n"/>
+      <c r="AC22" s="474" t="n"/>
+      <c r="AD22" s="474" t="n"/>
+      <c r="AE22" s="474" t="n"/>
+      <c r="AF22" s="474" t="n"/>
+      <c r="AG22" s="474" t="n"/>
+      <c r="AH22" s="474" t="n"/>
+      <c r="AI22" s="474" t="n"/>
+      <c r="AJ22" s="474" t="n"/>
+      <c r="AK22" s="474" t="n"/>
+      <c r="AL22" s="474" t="n"/>
+      <c r="AM22" s="474" t="n"/>
+      <c r="AN22" s="479" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1" s="264">
+      <c r="A23" s="480" t="inlineStr">
+        <is>
+          <t>NCR / Hold Ref (if Yellow/Red)</t>
+        </is>
+      </c>
+      <c r="B23" s="481" t="n"/>
+      <c r="C23" s="481" t="n"/>
+      <c r="D23" s="481" t="n"/>
+      <c r="E23" s="481" t="n"/>
+      <c r="F23" s="481" t="n"/>
+      <c r="G23" s="482" t="n"/>
+      <c r="H23" s="483" t="n"/>
+      <c r="I23" s="481" t="n"/>
+      <c r="J23" s="481" t="n"/>
+      <c r="K23" s="481" t="n"/>
+      <c r="L23" s="481" t="n"/>
+      <c r="M23" s="481" t="n"/>
+      <c r="N23" s="481" t="n"/>
+      <c r="O23" s="481" t="n"/>
+      <c r="P23" s="481" t="n"/>
+      <c r="Q23" s="481" t="n"/>
+      <c r="R23" s="481" t="n"/>
+      <c r="S23" s="481" t="n"/>
+      <c r="T23" s="482" t="n"/>
+      <c r="U23" s="484" t="inlineStr">
+        <is>
+          <t>Rework Order Ref (FRM-655)</t>
+        </is>
+      </c>
+      <c r="V23" s="481" t="n"/>
+      <c r="W23" s="481" t="n"/>
+      <c r="X23" s="481" t="n"/>
+      <c r="Y23" s="481" t="n"/>
+      <c r="Z23" s="481" t="n"/>
+      <c r="AA23" s="482" t="n"/>
+      <c r="AB23" s="485" t="n"/>
+      <c r="AC23" s="481" t="n"/>
+      <c r="AD23" s="481" t="n"/>
+      <c r="AE23" s="481" t="n"/>
+      <c r="AF23" s="481" t="n"/>
+      <c r="AG23" s="481" t="n"/>
+      <c r="AH23" s="481" t="n"/>
+      <c r="AI23" s="481" t="n"/>
+      <c r="AJ23" s="481" t="n"/>
+      <c r="AK23" s="481" t="n"/>
+      <c r="AL23" s="481" t="n"/>
+      <c r="AM23" s="481" t="n"/>
+      <c r="AN23" s="486" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1" s="264">
+      <c r="A24" s="487" t="inlineStr">
+        <is>
+          <t>Storage Location</t>
+        </is>
+      </c>
+      <c r="B24" s="488" t="n"/>
+      <c r="C24" s="488" t="n"/>
+      <c r="D24" s="488" t="n"/>
+      <c r="E24" s="488" t="n"/>
+      <c r="F24" s="488" t="n"/>
+      <c r="G24" s="489" t="n"/>
+      <c r="H24" s="490" t="n"/>
+      <c r="I24" s="488" t="n"/>
+      <c r="J24" s="488" t="n"/>
+      <c r="K24" s="488" t="n"/>
+      <c r="L24" s="488" t="n"/>
+      <c r="M24" s="488" t="n"/>
+      <c r="N24" s="488" t="n"/>
+      <c r="O24" s="488" t="n"/>
+      <c r="P24" s="488" t="n"/>
+      <c r="Q24" s="488" t="n"/>
+      <c r="R24" s="488" t="n"/>
+      <c r="S24" s="488" t="n"/>
+      <c r="T24" s="489" t="n"/>
+      <c r="U24" s="491" t="inlineStr">
+        <is>
+          <t>FIFO / Date Code</t>
+        </is>
+      </c>
+      <c r="V24" s="488" t="n"/>
+      <c r="W24" s="488" t="n"/>
+      <c r="X24" s="488" t="n"/>
+      <c r="Y24" s="488" t="n"/>
+      <c r="Z24" s="488" t="n"/>
+      <c r="AA24" s="489" t="n"/>
+      <c r="AB24" s="492" t="n"/>
+      <c r="AC24" s="488" t="n"/>
+      <c r="AD24" s="488" t="n"/>
+      <c r="AE24" s="488" t="n"/>
+      <c r="AF24" s="488" t="n"/>
+      <c r="AG24" s="488" t="n"/>
+      <c r="AH24" s="488" t="n"/>
+      <c r="AI24" s="488" t="n"/>
+      <c r="AJ24" s="488" t="n"/>
+      <c r="AK24" s="488" t="n"/>
+      <c r="AL24" s="488" t="n"/>
+      <c r="AM24" s="488" t="n"/>
+      <c r="AN24" s="493" t="n"/>
+    </row>
+    <row r="25" ht="4" customHeight="1" s="264">
+      <c r="A25" s="516" t="n"/>
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="26" t="n"/>
+      <c r="E25" s="26" t="n"/>
+      <c r="F25" s="26" t="n"/>
+      <c r="G25" s="26" t="n"/>
+      <c r="H25" s="26" t="n"/>
+      <c r="I25" s="26" t="n"/>
+      <c r="J25" s="26" t="n"/>
+      <c r="K25" s="26" t="n"/>
+      <c r="L25" s="26" t="n"/>
+      <c r="M25" s="26" t="n"/>
+      <c r="N25" s="26" t="n"/>
+      <c r="O25" s="26" t="n"/>
+      <c r="P25" s="26" t="n"/>
+      <c r="Q25" s="26" t="n"/>
+      <c r="R25" s="26" t="n"/>
+      <c r="S25" s="26" t="n"/>
+      <c r="T25" s="26" t="n"/>
+      <c r="U25" s="26" t="n"/>
+      <c r="V25" s="26" t="n"/>
+      <c r="W25" s="26" t="n"/>
+      <c r="X25" s="26" t="n"/>
+      <c r="Y25" s="26" t="n"/>
+      <c r="Z25" s="26" t="n"/>
+      <c r="AA25" s="26" t="n"/>
+      <c r="AB25" s="26" t="n"/>
+      <c r="AC25" s="26" t="n"/>
+      <c r="AD25" s="26" t="n"/>
+      <c r="AE25" s="26" t="n"/>
+      <c r="AF25" s="26" t="n"/>
+      <c r="AG25" s="26" t="n"/>
+      <c r="AH25" s="26" t="n"/>
+      <c r="AI25" s="26" t="n"/>
+      <c r="AJ25" s="26" t="n"/>
+      <c r="AK25" s="26" t="n"/>
+      <c r="AL25" s="26" t="n"/>
+      <c r="AM25" s="26" t="n"/>
+      <c r="AN25" s="26" t="n"/>
+    </row>
+    <row r="26" ht="17" customHeight="1" s="264">
+      <c r="A26" s="470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4.  STATUS CHANGE HISTORY</t>
+        </is>
+      </c>
+      <c r="B26" s="471" t="n"/>
+      <c r="C26" s="471" t="n"/>
+      <c r="D26" s="471" t="n"/>
+      <c r="E26" s="471" t="n"/>
+      <c r="F26" s="471" t="n"/>
+      <c r="G26" s="471" t="n"/>
+      <c r="H26" s="471" t="n"/>
+      <c r="I26" s="471" t="n"/>
+      <c r="J26" s="471" t="n"/>
+      <c r="K26" s="471" t="n"/>
+      <c r="L26" s="471" t="n"/>
+      <c r="M26" s="471" t="n"/>
+      <c r="N26" s="471" t="n"/>
+      <c r="O26" s="471" t="n"/>
+      <c r="P26" s="471" t="n"/>
+      <c r="Q26" s="471" t="n"/>
+      <c r="R26" s="471" t="n"/>
+      <c r="S26" s="471" t="n"/>
+      <c r="T26" s="471" t="n"/>
+      <c r="U26" s="471" t="n"/>
+      <c r="V26" s="471" t="n"/>
+      <c r="W26" s="471" t="n"/>
+      <c r="X26" s="471" t="n"/>
+      <c r="Y26" s="471" t="n"/>
+      <c r="Z26" s="471" t="n"/>
+      <c r="AA26" s="471" t="n"/>
+      <c r="AB26" s="471" t="n"/>
+      <c r="AC26" s="471" t="n"/>
+      <c r="AD26" s="471" t="n"/>
+      <c r="AE26" s="471" t="n"/>
+      <c r="AF26" s="471" t="n"/>
+      <c r="AG26" s="471" t="n"/>
+      <c r="AH26" s="471" t="n"/>
+      <c r="AI26" s="471" t="n"/>
+      <c r="AJ26" s="471" t="n"/>
+      <c r="AK26" s="471" t="n"/>
+      <c r="AL26" s="471" t="n"/>
+      <c r="AM26" s="471" t="n"/>
+      <c r="AN26" s="472" t="n"/>
+    </row>
+    <row r="27" ht="17" customHeight="1" s="264">
+      <c r="A27" s="494" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B27" s="475" t="n"/>
+      <c r="C27" s="495" t="inlineStr">
+        <is>
+          <t>Date / Time</t>
+        </is>
+      </c>
+      <c r="D27" s="474" t="n"/>
+      <c r="E27" s="475" t="n"/>
+      <c r="F27" s="495" t="inlineStr">
+        <is>
+          <t>From Status</t>
+        </is>
+      </c>
+      <c r="G27" s="474" t="n"/>
+      <c r="H27" s="474" t="n"/>
+      <c r="I27" s="474" t="n"/>
+      <c r="J27" s="474" t="n"/>
+      <c r="K27" s="474" t="n"/>
+      <c r="L27" s="474" t="n"/>
+      <c r="M27" s="474" t="n"/>
+      <c r="N27" s="474" t="n"/>
+      <c r="O27" s="474" t="n"/>
+      <c r="P27" s="474" t="n"/>
+      <c r="Q27" s="474" t="n"/>
+      <c r="R27" s="474" t="n"/>
+      <c r="S27" s="474" t="n"/>
+      <c r="T27" s="474" t="n"/>
+      <c r="U27" s="475" t="n"/>
+      <c r="V27" s="495" t="inlineStr">
+        <is>
+          <t>To Status</t>
+        </is>
+      </c>
+      <c r="W27" s="474" t="n"/>
+      <c r="X27" s="474" t="n"/>
+      <c r="Y27" s="474" t="n"/>
+      <c r="Z27" s="474" t="n"/>
+      <c r="AA27" s="474" t="n"/>
+      <c r="AB27" s="474" t="n"/>
+      <c r="AC27" s="474" t="n"/>
+      <c r="AD27" s="474" t="n"/>
+      <c r="AE27" s="475" t="n"/>
+      <c r="AF27" s="495" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="AG27" s="474" t="n"/>
+      <c r="AH27" s="474" t="n"/>
+      <c r="AI27" s="475" t="n"/>
+      <c r="AJ27" s="496" t="inlineStr">
+        <is>
+          <t>Changed By</t>
+        </is>
+      </c>
+      <c r="AK27" s="474" t="n"/>
+      <c r="AL27" s="474" t="n"/>
+      <c r="AM27" s="474" t="n"/>
+      <c r="AN27" s="479" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1" s="264">
+      <c r="A28" s="497">
+        <f>ROW()-ROW($A$28)+1</f>
+        <v/>
+      </c>
+      <c r="B28" s="482" t="n"/>
+      <c r="C28" s="498" t="n"/>
+      <c r="D28" s="481" t="n"/>
+      <c r="E28" s="482" t="n"/>
+      <c r="F28" s="499" t="n"/>
+      <c r="G28" s="481" t="n"/>
+      <c r="H28" s="481" t="n"/>
+      <c r="I28" s="481" t="n"/>
+      <c r="J28" s="481" t="n"/>
+      <c r="K28" s="481" t="n"/>
+      <c r="L28" s="481" t="n"/>
+      <c r="M28" s="481" t="n"/>
+      <c r="N28" s="481" t="n"/>
+      <c r="O28" s="481" t="n"/>
+      <c r="P28" s="481" t="n"/>
+      <c r="Q28" s="481" t="n"/>
+      <c r="R28" s="481" t="n"/>
+      <c r="S28" s="481" t="n"/>
+      <c r="T28" s="481" t="n"/>
+      <c r="U28" s="482" t="n"/>
+      <c r="V28" s="498" t="n"/>
+      <c r="W28" s="481" t="n"/>
+      <c r="X28" s="481" t="n"/>
+      <c r="Y28" s="481" t="n"/>
+      <c r="Z28" s="481" t="n"/>
+      <c r="AA28" s="481" t="n"/>
+      <c r="AB28" s="481" t="n"/>
+      <c r="AC28" s="481" t="n"/>
+      <c r="AD28" s="481" t="n"/>
+      <c r="AE28" s="482" t="n"/>
+      <c r="AF28" s="500" t="n"/>
+      <c r="AG28" s="481" t="n"/>
+      <c r="AH28" s="481" t="n"/>
+      <c r="AI28" s="482" t="n"/>
+      <c r="AJ28" s="501" t="n"/>
+      <c r="AK28" s="481" t="n"/>
+      <c r="AL28" s="481" t="n"/>
+      <c r="AM28" s="481" t="n"/>
+      <c r="AN28" s="486" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1" s="264">
+      <c r="A29" s="497">
+        <f>ROW()-ROW($A$28)+1</f>
+        <v/>
+      </c>
+      <c r="B29" s="482" t="n"/>
+      <c r="C29" s="498" t="n"/>
+      <c r="D29" s="481" t="n"/>
+      <c r="E29" s="482" t="n"/>
+      <c r="F29" s="502" t="n"/>
+      <c r="G29" s="481" t="n"/>
+      <c r="H29" s="481" t="n"/>
+      <c r="I29" s="481" t="n"/>
+      <c r="J29" s="481" t="n"/>
+      <c r="K29" s="481" t="n"/>
+      <c r="L29" s="481" t="n"/>
+      <c r="M29" s="481" t="n"/>
+      <c r="N29" s="481" t="n"/>
+      <c r="O29" s="481" t="n"/>
+      <c r="P29" s="481" t="n"/>
+      <c r="Q29" s="481" t="n"/>
+      <c r="R29" s="481" t="n"/>
+      <c r="S29" s="481" t="n"/>
+      <c r="T29" s="481" t="n"/>
+      <c r="U29" s="482" t="n"/>
+      <c r="V29" s="498" t="n"/>
+      <c r="W29" s="481" t="n"/>
+      <c r="X29" s="481" t="n"/>
+      <c r="Y29" s="481" t="n"/>
+      <c r="Z29" s="481" t="n"/>
+      <c r="AA29" s="481" t="n"/>
+      <c r="AB29" s="481" t="n"/>
+      <c r="AC29" s="481" t="n"/>
+      <c r="AD29" s="481" t="n"/>
+      <c r="AE29" s="482" t="n"/>
+      <c r="AF29" s="500" t="n"/>
+      <c r="AG29" s="481" t="n"/>
+      <c r="AH29" s="481" t="n"/>
+      <c r="AI29" s="482" t="n"/>
+      <c r="AJ29" s="501" t="n"/>
+      <c r="AK29" s="481" t="n"/>
+      <c r="AL29" s="481" t="n"/>
+      <c r="AM29" s="481" t="n"/>
+      <c r="AN29" s="486" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1" s="264">
+      <c r="A30" s="497">
+        <f>ROW()-ROW($A$28)+1</f>
+        <v/>
+      </c>
+      <c r="B30" s="482" t="n"/>
+      <c r="C30" s="498" t="n"/>
+      <c r="D30" s="481" t="n"/>
+      <c r="E30" s="482" t="n"/>
+      <c r="F30" s="499" t="n"/>
+      <c r="G30" s="481" t="n"/>
+      <c r="H30" s="481" t="n"/>
+      <c r="I30" s="481" t="n"/>
+      <c r="J30" s="481" t="n"/>
+      <c r="K30" s="481" t="n"/>
+      <c r="L30" s="481" t="n"/>
+      <c r="M30" s="481" t="n"/>
+      <c r="N30" s="481" t="n"/>
+      <c r="O30" s="481" t="n"/>
+      <c r="P30" s="481" t="n"/>
+      <c r="Q30" s="481" t="n"/>
+      <c r="R30" s="481" t="n"/>
+      <c r="S30" s="481" t="n"/>
+      <c r="T30" s="481" t="n"/>
+      <c r="U30" s="482" t="n"/>
+      <c r="V30" s="498" t="n"/>
+      <c r="W30" s="481" t="n"/>
+      <c r="X30" s="481" t="n"/>
+      <c r="Y30" s="481" t="n"/>
+      <c r="Z30" s="481" t="n"/>
+      <c r="AA30" s="481" t="n"/>
+      <c r="AB30" s="481" t="n"/>
+      <c r="AC30" s="481" t="n"/>
+      <c r="AD30" s="481" t="n"/>
+      <c r="AE30" s="482" t="n"/>
+      <c r="AF30" s="500" t="n"/>
+      <c r="AG30" s="481" t="n"/>
+      <c r="AH30" s="481" t="n"/>
+      <c r="AI30" s="482" t="n"/>
+      <c r="AJ30" s="501" t="n"/>
+      <c r="AK30" s="481" t="n"/>
+      <c r="AL30" s="481" t="n"/>
+      <c r="AM30" s="481" t="n"/>
+      <c r="AN30" s="486" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1" s="264">
+      <c r="A31" s="497">
+        <f>ROW()-ROW($A$28)+1</f>
+        <v/>
+      </c>
+      <c r="B31" s="482" t="n"/>
+      <c r="C31" s="498" t="n"/>
+      <c r="D31" s="481" t="n"/>
+      <c r="E31" s="482" t="n"/>
+      <c r="F31" s="502" t="n"/>
+      <c r="G31" s="481" t="n"/>
+      <c r="H31" s="481" t="n"/>
+      <c r="I31" s="481" t="n"/>
+      <c r="J31" s="481" t="n"/>
+      <c r="K31" s="481" t="n"/>
+      <c r="L31" s="481" t="n"/>
+      <c r="M31" s="481" t="n"/>
+      <c r="N31" s="481" t="n"/>
+      <c r="O31" s="481" t="n"/>
+      <c r="P31" s="481" t="n"/>
+      <c r="Q31" s="481" t="n"/>
+      <c r="R31" s="481" t="n"/>
+      <c r="S31" s="481" t="n"/>
+      <c r="T31" s="481" t="n"/>
+      <c r="U31" s="482" t="n"/>
+      <c r="V31" s="498" t="n"/>
+      <c r="W31" s="481" t="n"/>
+      <c r="X31" s="481" t="n"/>
+      <c r="Y31" s="481" t="n"/>
+      <c r="Z31" s="481" t="n"/>
+      <c r="AA31" s="481" t="n"/>
+      <c r="AB31" s="481" t="n"/>
+      <c r="AC31" s="481" t="n"/>
+      <c r="AD31" s="481" t="n"/>
+      <c r="AE31" s="482" t="n"/>
+      <c r="AF31" s="500" t="n"/>
+      <c r="AG31" s="481" t="n"/>
+      <c r="AH31" s="481" t="n"/>
+      <c r="AI31" s="482" t="n"/>
+      <c r="AJ31" s="501" t="n"/>
+      <c r="AK31" s="481" t="n"/>
+      <c r="AL31" s="481" t="n"/>
+      <c r="AM31" s="481" t="n"/>
+      <c r="AN31" s="486" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1" s="264">
+      <c r="A32" s="497">
+        <f>ROW()-ROW($A$28)+1</f>
+        <v/>
+      </c>
+      <c r="B32" s="482" t="n"/>
+      <c r="C32" s="498" t="n"/>
+      <c r="D32" s="481" t="n"/>
+      <c r="E32" s="482" t="n"/>
+      <c r="F32" s="499" t="n"/>
+      <c r="G32" s="481" t="n"/>
+      <c r="H32" s="481" t="n"/>
+      <c r="I32" s="481" t="n"/>
+      <c r="J32" s="481" t="n"/>
+      <c r="K32" s="481" t="n"/>
+      <c r="L32" s="481" t="n"/>
+      <c r="M32" s="481" t="n"/>
+      <c r="N32" s="481" t="n"/>
+      <c r="O32" s="481" t="n"/>
+      <c r="P32" s="481" t="n"/>
+      <c r="Q32" s="481" t="n"/>
+      <c r="R32" s="481" t="n"/>
+      <c r="S32" s="481" t="n"/>
+      <c r="T32" s="481" t="n"/>
+      <c r="U32" s="482" t="n"/>
+      <c r="V32" s="498" t="n"/>
+      <c r="W32" s="481" t="n"/>
+      <c r="X32" s="481" t="n"/>
+      <c r="Y32" s="481" t="n"/>
+      <c r="Z32" s="481" t="n"/>
+      <c r="AA32" s="481" t="n"/>
+      <c r="AB32" s="481" t="n"/>
+      <c r="AC32" s="481" t="n"/>
+      <c r="AD32" s="481" t="n"/>
+      <c r="AE32" s="482" t="n"/>
+      <c r="AF32" s="500" t="n"/>
+      <c r="AG32" s="481" t="n"/>
+      <c r="AH32" s="481" t="n"/>
+      <c r="AI32" s="482" t="n"/>
+      <c r="AJ32" s="501" t="n"/>
+      <c r="AK32" s="481" t="n"/>
+      <c r="AL32" s="481" t="n"/>
+      <c r="AM32" s="481" t="n"/>
+      <c r="AN32" s="486" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1" s="264">
+      <c r="A33" s="503">
+        <f>ROW()-ROW($A$28)+1</f>
+        <v/>
+      </c>
+      <c r="B33" s="489" t="n"/>
+      <c r="C33" s="504" t="n"/>
+      <c r="D33" s="488" t="n"/>
+      <c r="E33" s="489" t="n"/>
+      <c r="F33" s="505" t="n"/>
+      <c r="G33" s="488" t="n"/>
+      <c r="H33" s="488" t="n"/>
+      <c r="I33" s="488" t="n"/>
+      <c r="J33" s="488" t="n"/>
+      <c r="K33" s="488" t="n"/>
+      <c r="L33" s="488" t="n"/>
+      <c r="M33" s="488" t="n"/>
+      <c r="N33" s="488" t="n"/>
+      <c r="O33" s="488" t="n"/>
+      <c r="P33" s="488" t="n"/>
+      <c r="Q33" s="488" t="n"/>
+      <c r="R33" s="488" t="n"/>
+      <c r="S33" s="488" t="n"/>
+      <c r="T33" s="488" t="n"/>
+      <c r="U33" s="489" t="n"/>
+      <c r="V33" s="504" t="n"/>
+      <c r="W33" s="488" t="n"/>
+      <c r="X33" s="488" t="n"/>
+      <c r="Y33" s="488" t="n"/>
+      <c r="Z33" s="488" t="n"/>
+      <c r="AA33" s="488" t="n"/>
+      <c r="AB33" s="488" t="n"/>
+      <c r="AC33" s="488" t="n"/>
+      <c r="AD33" s="488" t="n"/>
+      <c r="AE33" s="489" t="n"/>
+      <c r="AF33" s="506" t="n"/>
+      <c r="AG33" s="488" t="n"/>
+      <c r="AH33" s="488" t="n"/>
+      <c r="AI33" s="489" t="n"/>
+      <c r="AJ33" s="507" t="n"/>
+      <c r="AK33" s="488" t="n"/>
+      <c r="AL33" s="488" t="n"/>
+      <c r="AM33" s="488" t="n"/>
+      <c r="AN33" s="493" t="n"/>
+    </row>
+    <row r="34" ht="4" customHeight="1" s="264">
+      <c r="A34" s="516" t="n"/>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+      <c r="E34" s="26" t="n"/>
+      <c r="F34" s="26" t="n"/>
+      <c r="G34" s="26" t="n"/>
+      <c r="H34" s="26" t="n"/>
+      <c r="I34" s="26" t="n"/>
+      <c r="J34" s="26" t="n"/>
+      <c r="K34" s="26" t="n"/>
+      <c r="L34" s="26" t="n"/>
+      <c r="M34" s="26" t="n"/>
+      <c r="N34" s="26" t="n"/>
+      <c r="O34" s="26" t="n"/>
+      <c r="P34" s="26" t="n"/>
+      <c r="Q34" s="26" t="n"/>
+      <c r="R34" s="26" t="n"/>
+      <c r="S34" s="26" t="n"/>
+      <c r="T34" s="26" t="n"/>
+      <c r="U34" s="26" t="n"/>
+      <c r="V34" s="26" t="n"/>
+      <c r="W34" s="26" t="n"/>
+      <c r="X34" s="26" t="n"/>
+      <c r="Y34" s="26" t="n"/>
+      <c r="Z34" s="26" t="n"/>
+      <c r="AA34" s="26" t="n"/>
+      <c r="AB34" s="26" t="n"/>
+      <c r="AC34" s="26" t="n"/>
+      <c r="AD34" s="26" t="n"/>
+      <c r="AE34" s="26" t="n"/>
+      <c r="AF34" s="26" t="n"/>
+      <c r="AG34" s="26" t="n"/>
+      <c r="AH34" s="26" t="n"/>
+      <c r="AI34" s="26" t="n"/>
+      <c r="AJ34" s="26" t="n"/>
+      <c r="AK34" s="26" t="n"/>
+      <c r="AL34" s="26" t="n"/>
+      <c r="AM34" s="26" t="n"/>
+      <c r="AN34" s="26" t="n"/>
+    </row>
+    <row r="35" ht="17" customHeight="1" s="264">
+      <c r="A35" s="470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5.  APPROVAL</t>
+        </is>
+      </c>
+      <c r="B35" s="471" t="n"/>
+      <c r="C35" s="471" t="n"/>
+      <c r="D35" s="471" t="n"/>
+      <c r="E35" s="471" t="n"/>
+      <c r="F35" s="471" t="n"/>
+      <c r="G35" s="471" t="n"/>
+      <c r="H35" s="471" t="n"/>
+      <c r="I35" s="471" t="n"/>
+      <c r="J35" s="471" t="n"/>
+      <c r="K35" s="471" t="n"/>
+      <c r="L35" s="471" t="n"/>
+      <c r="M35" s="471" t="n"/>
+      <c r="N35" s="471" t="n"/>
+      <c r="O35" s="471" t="n"/>
+      <c r="P35" s="471" t="n"/>
+      <c r="Q35" s="471" t="n"/>
+      <c r="R35" s="471" t="n"/>
+      <c r="S35" s="471" t="n"/>
+      <c r="T35" s="471" t="n"/>
+      <c r="U35" s="471" t="n"/>
+      <c r="V35" s="471" t="n"/>
+      <c r="W35" s="471" t="n"/>
+      <c r="X35" s="471" t="n"/>
+      <c r="Y35" s="471" t="n"/>
+      <c r="Z35" s="471" t="n"/>
+      <c r="AA35" s="471" t="n"/>
+      <c r="AB35" s="471" t="n"/>
+      <c r="AC35" s="471" t="n"/>
+      <c r="AD35" s="471" t="n"/>
+      <c r="AE35" s="471" t="n"/>
+      <c r="AF35" s="471" t="n"/>
+      <c r="AG35" s="471" t="n"/>
+      <c r="AH35" s="471" t="n"/>
+      <c r="AI35" s="471" t="n"/>
+      <c r="AJ35" s="471" t="n"/>
+      <c r="AK35" s="471" t="n"/>
+      <c r="AL35" s="471" t="n"/>
+      <c r="AM35" s="471" t="n"/>
+      <c r="AN35" s="472" t="n"/>
+    </row>
+    <row r="36" ht="17" customHeight="1" s="264">
+      <c r="A36" s="508" t="inlineStr">
         <is>
           <t>Operator</t>
         </is>
       </c>
-      <c r="B15" s="471" t="n"/>
-      <c r="C15" s="471" t="n"/>
-      <c r="D15" s="471" t="n"/>
-      <c r="E15" s="471" t="n"/>
-      <c r="F15" s="471" t="n"/>
-      <c r="G15" s="471" t="n"/>
-      <c r="H15" s="471" t="n"/>
-      <c r="I15" s="471" t="n"/>
-      <c r="J15" s="471" t="n"/>
-      <c r="K15" s="471" t="n"/>
-      <c r="L15" s="471" t="n"/>
-      <c r="M15" s="471" t="n"/>
-      <c r="N15" s="471" t="n"/>
-      <c r="O15" s="471" t="n"/>
-      <c r="P15" s="471" t="n"/>
-      <c r="Q15" s="471" t="n"/>
-      <c r="R15" s="471" t="n"/>
-      <c r="S15" s="471" t="n"/>
-      <c r="T15" s="472" t="n"/>
-      <c r="U15" s="494" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-      <c r="V15" s="471" t="n"/>
-      <c r="W15" s="471" t="n"/>
-      <c r="X15" s="471" t="n"/>
-      <c r="Y15" s="471" t="n"/>
-      <c r="Z15" s="471" t="n"/>
-      <c r="AA15" s="471" t="n"/>
-      <c r="AB15" s="471" t="n"/>
-      <c r="AC15" s="471" t="n"/>
-      <c r="AD15" s="471" t="n"/>
-      <c r="AE15" s="471" t="n"/>
-      <c r="AF15" s="471" t="n"/>
-      <c r="AG15" s="471" t="n"/>
-      <c r="AH15" s="471" t="n"/>
-      <c r="AI15" s="471" t="n"/>
-      <c r="AJ15" s="471" t="n"/>
-      <c r="AK15" s="471" t="n"/>
-      <c r="AL15" s="471" t="n"/>
-      <c r="AM15" s="471" t="n"/>
-      <c r="AN15" s="472" t="n"/>
+      <c r="B36" s="471" t="n"/>
+      <c r="C36" s="471" t="n"/>
+      <c r="D36" s="471" t="n"/>
+      <c r="E36" s="471" t="n"/>
+      <c r="F36" s="471" t="n"/>
+      <c r="G36" s="471" t="n"/>
+      <c r="H36" s="471" t="n"/>
+      <c r="I36" s="471" t="n"/>
+      <c r="J36" s="471" t="n"/>
+      <c r="K36" s="471" t="n"/>
+      <c r="L36" s="471" t="n"/>
+      <c r="M36" s="472" t="n"/>
+      <c r="N36" s="508" t="inlineStr">
+        <is>
+          <t>QC Inspector</t>
+        </is>
+      </c>
+      <c r="O36" s="471" t="n"/>
+      <c r="P36" s="471" t="n"/>
+      <c r="Q36" s="471" t="n"/>
+      <c r="R36" s="471" t="n"/>
+      <c r="S36" s="471" t="n"/>
+      <c r="T36" s="471" t="n"/>
+      <c r="U36" s="471" t="n"/>
+      <c r="V36" s="471" t="n"/>
+      <c r="W36" s="471" t="n"/>
+      <c r="X36" s="471" t="n"/>
+      <c r="Y36" s="471" t="n"/>
+      <c r="Z36" s="472" t="n"/>
+      <c r="AA36" s="508" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="AB36" s="471" t="n"/>
+      <c r="AC36" s="471" t="n"/>
+      <c r="AD36" s="471" t="n"/>
+      <c r="AE36" s="471" t="n"/>
+      <c r="AF36" s="471" t="n"/>
+      <c r="AG36" s="471" t="n"/>
+      <c r="AH36" s="471" t="n"/>
+      <c r="AI36" s="471" t="n"/>
+      <c r="AJ36" s="471" t="n"/>
+      <c r="AK36" s="471" t="n"/>
+      <c r="AL36" s="471" t="n"/>
+      <c r="AM36" s="471" t="n"/>
+      <c r="AN36" s="472" t="n"/>
     </row>
-    <row r="16" ht="26" customHeight="1" s="264">
-      <c r="A16" s="495" t="inlineStr">
+    <row r="37" ht="26" customHeight="1" s="264">
+      <c r="A37" s="509" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="B16" s="496" t="n"/>
-      <c r="C16" s="496" t="n"/>
-      <c r="D16" s="496" t="n"/>
-      <c r="E16" s="496" t="n"/>
-      <c r="F16" s="496" t="n"/>
-      <c r="G16" s="496" t="n"/>
-      <c r="H16" s="496" t="n"/>
-      <c r="I16" s="496" t="n"/>
-      <c r="J16" s="496" t="n"/>
-      <c r="K16" s="496" t="n"/>
-      <c r="L16" s="496" t="n"/>
-      <c r="M16" s="496" t="n"/>
-      <c r="N16" s="496" t="n"/>
-      <c r="O16" s="496" t="n"/>
-      <c r="P16" s="496" t="n"/>
-      <c r="Q16" s="496" t="n"/>
-      <c r="R16" s="496" t="n"/>
-      <c r="S16" s="496" t="n"/>
-      <c r="T16" s="497" t="n"/>
-      <c r="U16" s="495" t="inlineStr">
+      <c r="B37" s="510" t="n"/>
+      <c r="C37" s="510" t="n"/>
+      <c r="D37" s="510" t="n"/>
+      <c r="E37" s="510" t="n"/>
+      <c r="F37" s="510" t="n"/>
+      <c r="G37" s="510" t="n"/>
+      <c r="H37" s="510" t="n"/>
+      <c r="I37" s="510" t="n"/>
+      <c r="J37" s="510" t="n"/>
+      <c r="K37" s="510" t="n"/>
+      <c r="L37" s="510" t="n"/>
+      <c r="M37" s="511" t="n"/>
+      <c r="N37" s="509" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="V16" s="496" t="n"/>
-      <c r="W16" s="496" t="n"/>
-      <c r="X16" s="496" t="n"/>
-      <c r="Y16" s="496" t="n"/>
-      <c r="Z16" s="496" t="n"/>
-      <c r="AA16" s="496" t="n"/>
-      <c r="AB16" s="496" t="n"/>
-      <c r="AC16" s="496" t="n"/>
-      <c r="AD16" s="496" t="n"/>
-      <c r="AE16" s="496" t="n"/>
-      <c r="AF16" s="496" t="n"/>
-      <c r="AG16" s="496" t="n"/>
-      <c r="AH16" s="496" t="n"/>
-      <c r="AI16" s="496" t="n"/>
-      <c r="AJ16" s="496" t="n"/>
-      <c r="AK16" s="496" t="n"/>
-      <c r="AL16" s="496" t="n"/>
-      <c r="AM16" s="496" t="n"/>
-      <c r="AN16" s="497" t="n"/>
+      <c r="O37" s="510" t="n"/>
+      <c r="P37" s="510" t="n"/>
+      <c r="Q37" s="510" t="n"/>
+      <c r="R37" s="510" t="n"/>
+      <c r="S37" s="510" t="n"/>
+      <c r="T37" s="510" t="n"/>
+      <c r="U37" s="510" t="n"/>
+      <c r="V37" s="510" t="n"/>
+      <c r="W37" s="510" t="n"/>
+      <c r="X37" s="510" t="n"/>
+      <c r="Y37" s="510" t="n"/>
+      <c r="Z37" s="511" t="n"/>
+      <c r="AA37" s="509" t="inlineStr">
+        <is>
+          <t>Name  /  Signature  /  Date</t>
+        </is>
+      </c>
+      <c r="AB37" s="510" t="n"/>
+      <c r="AC37" s="510" t="n"/>
+      <c r="AD37" s="510" t="n"/>
+      <c r="AE37" s="510" t="n"/>
+      <c r="AF37" s="510" t="n"/>
+      <c r="AG37" s="510" t="n"/>
+      <c r="AH37" s="510" t="n"/>
+      <c r="AI37" s="510" t="n"/>
+      <c r="AJ37" s="510" t="n"/>
+      <c r="AK37" s="510" t="n"/>
+      <c r="AL37" s="510" t="n"/>
+      <c r="AM37" s="510" t="n"/>
+      <c r="AN37" s="511" t="n"/>
     </row>
-    <row r="17" ht="26" customHeight="1" s="264">
-      <c r="A17" s="498" t="n"/>
-      <c r="T17" s="499" t="n"/>
-      <c r="U17" s="498" t="n"/>
-      <c r="AN17" s="499" t="n"/>
+    <row r="38" ht="26" customHeight="1" s="264">
+      <c r="A38" s="512" t="n"/>
+      <c r="M38" s="513" t="n"/>
+      <c r="N38" s="512" t="n"/>
+      <c r="Z38" s="513" t="n"/>
+      <c r="AA38" s="512" t="n"/>
+      <c r="AN38" s="513" t="n"/>
     </row>
-    <row r="18" ht="26" customHeight="1" s="264">
-      <c r="A18" s="500" t="n"/>
-      <c r="B18" s="488" t="n"/>
-      <c r="C18" s="488" t="n"/>
-      <c r="D18" s="488" t="n"/>
-      <c r="E18" s="488" t="n"/>
-      <c r="F18" s="488" t="n"/>
-      <c r="G18" s="488" t="n"/>
-      <c r="H18" s="488" t="n"/>
-      <c r="I18" s="488" t="n"/>
-      <c r="J18" s="488" t="n"/>
-      <c r="K18" s="488" t="n"/>
-      <c r="L18" s="488" t="n"/>
-      <c r="M18" s="488" t="n"/>
-      <c r="N18" s="488" t="n"/>
-      <c r="O18" s="488" t="n"/>
-      <c r="P18" s="488" t="n"/>
-      <c r="Q18" s="488" t="n"/>
-      <c r="R18" s="488" t="n"/>
-      <c r="S18" s="488" t="n"/>
-      <c r="T18" s="493" t="n"/>
-      <c r="U18" s="500" t="n"/>
-      <c r="V18" s="488" t="n"/>
-      <c r="W18" s="488" t="n"/>
-      <c r="X18" s="488" t="n"/>
-      <c r="Y18" s="488" t="n"/>
-      <c r="Z18" s="488" t="n"/>
-      <c r="AA18" s="488" t="n"/>
-      <c r="AB18" s="488" t="n"/>
-      <c r="AC18" s="488" t="n"/>
-      <c r="AD18" s="488" t="n"/>
-      <c r="AE18" s="488" t="n"/>
-      <c r="AF18" s="488" t="n"/>
-      <c r="AG18" s="488" t="n"/>
-      <c r="AH18" s="488" t="n"/>
-      <c r="AI18" s="488" t="n"/>
-      <c r="AJ18" s="488" t="n"/>
-      <c r="AK18" s="488" t="n"/>
-      <c r="AL18" s="488" t="n"/>
-      <c r="AM18" s="488" t="n"/>
-      <c r="AN18" s="493" t="n"/>
+    <row r="39" ht="26" customHeight="1" s="264">
+      <c r="A39" s="514" t="n"/>
+      <c r="B39" s="488" t="n"/>
+      <c r="C39" s="488" t="n"/>
+      <c r="D39" s="488" t="n"/>
+      <c r="E39" s="488" t="n"/>
+      <c r="F39" s="488" t="n"/>
+      <c r="G39" s="488" t="n"/>
+      <c r="H39" s="488" t="n"/>
+      <c r="I39" s="488" t="n"/>
+      <c r="J39" s="488" t="n"/>
+      <c r="K39" s="488" t="n"/>
+      <c r="L39" s="488" t="n"/>
+      <c r="M39" s="493" t="n"/>
+      <c r="N39" s="514" t="n"/>
+      <c r="O39" s="488" t="n"/>
+      <c r="P39" s="488" t="n"/>
+      <c r="Q39" s="488" t="n"/>
+      <c r="R39" s="488" t="n"/>
+      <c r="S39" s="488" t="n"/>
+      <c r="T39" s="488" t="n"/>
+      <c r="U39" s="488" t="n"/>
+      <c r="V39" s="488" t="n"/>
+      <c r="W39" s="488" t="n"/>
+      <c r="X39" s="488" t="n"/>
+      <c r="Y39" s="488" t="n"/>
+      <c r="Z39" s="493" t="n"/>
+      <c r="AA39" s="514" t="n"/>
+      <c r="AB39" s="488" t="n"/>
+      <c r="AC39" s="488" t="n"/>
+      <c r="AD39" s="488" t="n"/>
+      <c r="AE39" s="488" t="n"/>
+      <c r="AF39" s="488" t="n"/>
+      <c r="AG39" s="488" t="n"/>
+      <c r="AH39" s="488" t="n"/>
+      <c r="AI39" s="488" t="n"/>
+      <c r="AJ39" s="488" t="n"/>
+      <c r="AK39" s="488" t="n"/>
+      <c r="AL39" s="488" t="n"/>
+      <c r="AM39" s="488" t="n"/>
+      <c r="AN39" s="493" t="n"/>
     </row>
-    <row r="19" ht="4" customHeight="1" s="264">
-      <c r="A19" s="469" t="n"/>
-      <c r="B19" s="26" t="n"/>
-      <c r="C19" s="26" t="n"/>
-      <c r="D19" s="26" t="n"/>
-      <c r="E19" s="26" t="n"/>
-      <c r="F19" s="26" t="n"/>
-      <c r="G19" s="26" t="n"/>
-      <c r="H19" s="26" t="n"/>
-      <c r="I19" s="26" t="n"/>
-      <c r="J19" s="26" t="n"/>
-      <c r="K19" s="26" t="n"/>
-      <c r="L19" s="26" t="n"/>
-      <c r="M19" s="26" t="n"/>
-      <c r="N19" s="26" t="n"/>
-      <c r="O19" s="26" t="n"/>
-      <c r="P19" s="26" t="n"/>
-      <c r="Q19" s="26" t="n"/>
-      <c r="R19" s="26" t="n"/>
-      <c r="S19" s="26" t="n"/>
-      <c r="T19" s="26" t="n"/>
-      <c r="U19" s="26" t="n"/>
-      <c r="V19" s="26" t="n"/>
-      <c r="W19" s="26" t="n"/>
-      <c r="X19" s="26" t="n"/>
-      <c r="Y19" s="26" t="n"/>
-      <c r="Z19" s="26" t="n"/>
-      <c r="AA19" s="26" t="n"/>
-      <c r="AB19" s="26" t="n"/>
-      <c r="AC19" s="26" t="n"/>
-      <c r="AD19" s="26" t="n"/>
-      <c r="AE19" s="26" t="n"/>
-      <c r="AF19" s="26" t="n"/>
-      <c r="AG19" s="26" t="n"/>
-      <c r="AH19" s="26" t="n"/>
-      <c r="AI19" s="26" t="n"/>
-      <c r="AJ19" s="26" t="n"/>
-      <c r="AK19" s="26" t="n"/>
-      <c r="AL19" s="26" t="n"/>
-      <c r="AM19" s="26" t="n"/>
-      <c r="AN19" s="26" t="n"/>
+    <row r="40" ht="4" customHeight="1" s="264">
+      <c r="A40" s="516" t="n"/>
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+      <c r="E40" s="26" t="n"/>
+      <c r="F40" s="26" t="n"/>
+      <c r="G40" s="26" t="n"/>
+      <c r="H40" s="26" t="n"/>
+      <c r="I40" s="26" t="n"/>
+      <c r="J40" s="26" t="n"/>
+      <c r="K40" s="26" t="n"/>
+      <c r="L40" s="26" t="n"/>
+      <c r="M40" s="26" t="n"/>
+      <c r="N40" s="26" t="n"/>
+      <c r="O40" s="26" t="n"/>
+      <c r="P40" s="26" t="n"/>
+      <c r="Q40" s="26" t="n"/>
+      <c r="R40" s="26" t="n"/>
+      <c r="S40" s="26" t="n"/>
+      <c r="T40" s="26" t="n"/>
+      <c r="U40" s="26" t="n"/>
+      <c r="V40" s="26" t="n"/>
+      <c r="W40" s="26" t="n"/>
+      <c r="X40" s="26" t="n"/>
+      <c r="Y40" s="26" t="n"/>
+      <c r="Z40" s="26" t="n"/>
+      <c r="AA40" s="26" t="n"/>
+      <c r="AB40" s="26" t="n"/>
+      <c r="AC40" s="26" t="n"/>
+      <c r="AD40" s="26" t="n"/>
+      <c r="AE40" s="26" t="n"/>
+      <c r="AF40" s="26" t="n"/>
+      <c r="AG40" s="26" t="n"/>
+      <c r="AH40" s="26" t="n"/>
+      <c r="AI40" s="26" t="n"/>
+      <c r="AJ40" s="26" t="n"/>
+      <c r="AK40" s="26" t="n"/>
+      <c r="AL40" s="26" t="n"/>
+      <c r="AM40" s="26" t="n"/>
+      <c r="AN40" s="26" t="n"/>
     </row>
-    <row r="20" ht="24" customHeight="1" s="264">
-      <c r="A20" s="501" t="inlineStr">
-        <is>
-          <t>NOTICE — Attach to WIP container. Update status at each operation.</t>
-        </is>
-      </c>
-      <c r="B20" s="471" t="n"/>
-      <c r="C20" s="471" t="n"/>
-      <c r="D20" s="471" t="n"/>
-      <c r="E20" s="471" t="n"/>
-      <c r="F20" s="471" t="n"/>
-      <c r="G20" s="471" t="n"/>
-      <c r="H20" s="471" t="n"/>
-      <c r="I20" s="471" t="n"/>
-      <c r="J20" s="471" t="n"/>
-      <c r="K20" s="471" t="n"/>
-      <c r="L20" s="471" t="n"/>
-      <c r="M20" s="471" t="n"/>
-      <c r="N20" s="471" t="n"/>
-      <c r="O20" s="471" t="n"/>
-      <c r="P20" s="471" t="n"/>
-      <c r="Q20" s="471" t="n"/>
-      <c r="R20" s="471" t="n"/>
-      <c r="S20" s="471" t="n"/>
-      <c r="T20" s="471" t="n"/>
-      <c r="U20" s="471" t="n"/>
-      <c r="V20" s="471" t="n"/>
-      <c r="W20" s="471" t="n"/>
-      <c r="X20" s="471" t="n"/>
-      <c r="Y20" s="471" t="n"/>
-      <c r="Z20" s="471" t="n"/>
-      <c r="AA20" s="471" t="n"/>
-      <c r="AB20" s="471" t="n"/>
-      <c r="AC20" s="471" t="n"/>
-      <c r="AD20" s="471" t="n"/>
-      <c r="AE20" s="471" t="n"/>
-      <c r="AF20" s="471" t="n"/>
-      <c r="AG20" s="471" t="n"/>
-      <c r="AH20" s="471" t="n"/>
-      <c r="AI20" s="471" t="n"/>
-      <c r="AJ20" s="471" t="n"/>
-      <c r="AK20" s="471" t="n"/>
-      <c r="AL20" s="471" t="n"/>
-      <c r="AM20" s="471" t="n"/>
-      <c r="AN20" s="472" t="n"/>
+    <row r="41" ht="24" customHeight="1" s="264">
+      <c r="A41" s="515" t="inlineStr">
+        <is>
+          <t>NOTICE — One tag accompanies every WIP tray / container and is updated at each operation. The tag colour status must always match the physical tray colour (WI-703). This tag supersedes the former FRM-722 Product ID Tag. Ref: WI-703 / SOP-502. Retain: with the lot. Enter data only in white input cells. Do not add, delete or resize columns/rows.</t>
+        </is>
+      </c>
+      <c r="B41" s="471" t="n"/>
+      <c r="C41" s="471" t="n"/>
+      <c r="D41" s="471" t="n"/>
+      <c r="E41" s="471" t="n"/>
+      <c r="F41" s="471" t="n"/>
+      <c r="G41" s="471" t="n"/>
+      <c r="H41" s="471" t="n"/>
+      <c r="I41" s="471" t="n"/>
+      <c r="J41" s="471" t="n"/>
+      <c r="K41" s="471" t="n"/>
+      <c r="L41" s="471" t="n"/>
+      <c r="M41" s="471" t="n"/>
+      <c r="N41" s="471" t="n"/>
+      <c r="O41" s="471" t="n"/>
+      <c r="P41" s="471" t="n"/>
+      <c r="Q41" s="471" t="n"/>
+      <c r="R41" s="471" t="n"/>
+      <c r="S41" s="471" t="n"/>
+      <c r="T41" s="471" t="n"/>
+      <c r="U41" s="471" t="n"/>
+      <c r="V41" s="471" t="n"/>
+      <c r="W41" s="471" t="n"/>
+      <c r="X41" s="471" t="n"/>
+      <c r="Y41" s="471" t="n"/>
+      <c r="Z41" s="471" t="n"/>
+      <c r="AA41" s="471" t="n"/>
+      <c r="AB41" s="471" t="n"/>
+      <c r="AC41" s="471" t="n"/>
+      <c r="AD41" s="471" t="n"/>
+      <c r="AE41" s="471" t="n"/>
+      <c r="AF41" s="471" t="n"/>
+      <c r="AG41" s="471" t="n"/>
+      <c r="AH41" s="471" t="n"/>
+      <c r="AI41" s="471" t="n"/>
+      <c r="AJ41" s="471" t="n"/>
+      <c r="AK41" s="471" t="n"/>
+      <c r="AL41" s="471" t="n"/>
+      <c r="AM41" s="471" t="n"/>
+      <c r="AN41" s="472" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="AI6:AN6"/>
+  <mergeCells count="122">
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A21:AN21"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="AB17:AN17"/>
+    <mergeCell ref="AE6:AH6"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="U19:AA19"/>
+    <mergeCell ref="U14:AA14"/>
+    <mergeCell ref="AB19:AN19"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="N36:Z36"/>
+    <mergeCell ref="U9:AA9"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A40:AN40"/>
+    <mergeCell ref="AB14:AN14"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="H9:T9"/>
+    <mergeCell ref="I2:AD4"/>
+    <mergeCell ref="F30:U30"/>
+    <mergeCell ref="F33:U33"/>
+    <mergeCell ref="N37:Z39"/>
+    <mergeCell ref="A2:H6"/>
+    <mergeCell ref="A16:AN16"/>
+    <mergeCell ref="U13:AA13"/>
+    <mergeCell ref="AJ29:AN29"/>
+    <mergeCell ref="A25:AN25"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="AJ31:AN31"/>
+    <mergeCell ref="U24:AA24"/>
+    <mergeCell ref="V27:AE27"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="U18:AA18"/>
+    <mergeCell ref="AB23:AN23"/>
+    <mergeCell ref="F28:U28"/>
+    <mergeCell ref="F31:U31"/>
+    <mergeCell ref="H13:T13"/>
+    <mergeCell ref="AF32:AI32"/>
     <mergeCell ref="I5:AD5"/>
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="H12:T12"/>
-    <mergeCell ref="AI4:AN4"/>
-    <mergeCell ref="AE6:AH6"/>
-    <mergeCell ref="A14:AN14"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="U15:AN15"/>
     <mergeCell ref="AE5:AH5"/>
-    <mergeCell ref="A8:AN8"/>
+    <mergeCell ref="H24:T24"/>
     <mergeCell ref="U10:AA10"/>
     <mergeCell ref="AB10:AN10"/>
-    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="H18:T18"/>
     <mergeCell ref="A20:AN20"/>
-    <mergeCell ref="AE4:AH4"/>
-    <mergeCell ref="U9:AA9"/>
-    <mergeCell ref="A19:AN19"/>
-    <mergeCell ref="A13:AN13"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="AB18:AN18"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="AA36:AN36"/>
     <mergeCell ref="AI3:AN3"/>
-    <mergeCell ref="I6:AD6"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="AF33:AI33"/>
     <mergeCell ref="H10:T10"/>
-    <mergeCell ref="AI2:AN2"/>
-    <mergeCell ref="H9:T9"/>
-    <mergeCell ref="A16:T18"/>
-    <mergeCell ref="I2:AD4"/>
-    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="A15:AN15"/>
     <mergeCell ref="AI5:AN5"/>
-    <mergeCell ref="U16:AN18"/>
-    <mergeCell ref="AE2:AH2"/>
-    <mergeCell ref="U11:AA11"/>
-    <mergeCell ref="A2:H6"/>
-    <mergeCell ref="AB9:AN9"/>
+    <mergeCell ref="AJ33:AN33"/>
+    <mergeCell ref="V29:AE29"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="V31:AE31"/>
+    <mergeCell ref="AB22:AN22"/>
     <mergeCell ref="A7:AN7"/>
     <mergeCell ref="A12:G12"/>
+    <mergeCell ref="H17:T17"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="A41:AN41"/>
     <mergeCell ref="U12:AA12"/>
     <mergeCell ref="AB12:AN12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="H19:T19"/>
+    <mergeCell ref="V32:AE32"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="H12:T12"/>
+    <mergeCell ref="AB13:AN13"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="A35:AN35"/>
+    <mergeCell ref="H14:T14"/>
+    <mergeCell ref="H23:T23"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="V33:AE33"/>
+    <mergeCell ref="AB24:AN24"/>
+    <mergeCell ref="I6:AD6"/>
+    <mergeCell ref="A36:M36"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="U17:AA17"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="U11:AA11"/>
+    <mergeCell ref="V28:AE28"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="F32:U32"/>
+    <mergeCell ref="AB9:AN9"/>
+    <mergeCell ref="V30:AE30"/>
     <mergeCell ref="H11:T11"/>
+    <mergeCell ref="A37:M39"/>
     <mergeCell ref="AB11:AN11"/>
+    <mergeCell ref="AI6:AN6"/>
+    <mergeCell ref="H22:T22"/>
+    <mergeCell ref="A26:AN26"/>
+    <mergeCell ref="F27:U27"/>
+    <mergeCell ref="AJ27:AN27"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="U23:AA23"/>
+    <mergeCell ref="A8:AN8"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="AA37:AN39"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="U22:AA22"/>
+    <mergeCell ref="AJ28:AN28"/>
+    <mergeCell ref="F29:U29"/>
+    <mergeCell ref="A34:AN34"/>
+    <mergeCell ref="AJ30:AN30"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="AJ32:AN32"/>
+    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
